--- a/output/tables/GD/finished tables/Temporal_GD_Table.xlsx
+++ b/output/tables/GD/finished tables/Temporal_GD_Table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\R_WD\revised_bison_popgen\output\tables\GD\finished tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\D_RWD\revised_bison_popgen\output\tables\GD\finished tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{3CC7E853-C2EC-4DF0-8CBC-914230518F62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{974CF91E-4A48-4A02-8817-C2FC67576EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-118" yWindow="-118" windowWidth="20343" windowHeight="12934" xr2:uid="{A0AEF7AD-496E-4010-99D7-757C33A53E96}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A0AEF7AD-496E-4010-99D7-757C33A53E96}"/>
   </bookViews>
   <sheets>
     <sheet name="Temporal_GD_Table" sheetId="1" r:id="rId1"/>
@@ -329,9 +329,6 @@
     <t>0.59 ± 0.27</t>
   </si>
   <si>
-    <t>6.62 ± 2.06</t>
-  </si>
-  <si>
     <t>0.64 ± 0.11</t>
   </si>
   <si>
@@ -411,6 +408,9 @@
   </si>
   <si>
     <t>3.39 ± 0.70</t>
+  </si>
+  <si>
+    <t>n/a</t>
   </si>
 </sst>
 </file>
@@ -789,7 +789,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -907,10 +907,8 @@
     <border>
       <left/>
       <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
+      <top/>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -918,16 +916,9 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -978,60 +969,87 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="24" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="23" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="18" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="18" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="18" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="24" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="33" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="24" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1410,841 +1428,842 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFA4CB0B-A2A6-4B1F-9B7D-925F8B80628E}">
   <dimension ref="A1:G36"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="11" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="3"/>
+    <col min="1" max="1" width="16.28515625" style="2" customWidth="1"/>
+    <col min="2" max="3" width="15.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17.7" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="17" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="1">
         <v>63</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="9">
         <v>20</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="F3" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="G3" s="10">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1">
+        <v>79</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="14">
-        <v>-0.04</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="G4" s="3">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1">
+        <v>21</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="3">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C6" s="9">
+        <v>12</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="10">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="9">
+        <v>31</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="10">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1">
+        <v>33</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="1">
+        <v>21</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="9">
+        <v>81</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="G10" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="9">
+        <v>25</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="10">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="1">
+        <v>8</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="9">
+        <v>7</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="G13" s="10">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="9">
+        <v>17</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G14" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="1">
+        <v>19</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="1">
+        <v>29</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G16" s="3">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="9">
+        <v>10</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G17" s="10">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="9">
+        <v>9</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="G18" s="10">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="1">
+        <v>10</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20" s="1">
+        <v>26</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="9">
+        <v>23</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G21" s="11">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="9">
+        <v>74</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G22" s="11">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="1">
+        <v>11</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="1">
+        <v>35</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G24" s="3">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="9">
+        <v>18</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="G25" s="10">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26" s="9">
+        <v>24</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G26" s="10">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="1">
+        <v>25</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28" s="1">
+        <v>43</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="G4" s="7">
+      <c r="G28" s="7">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="9">
+        <v>5</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="G29" s="10">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B30" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="C30" s="22">
+        <v>4</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="E30" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="F30" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="G30" s="23">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="25">
+        <v>29</v>
+      </c>
+      <c r="D31" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="E31" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="F31" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="G31" s="26">
         <v>0.01</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="s">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B32" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C32" s="19">
+        <v>59</v>
+      </c>
+      <c r="D32" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="F32" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="G32" s="20">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="9">
+        <v>40</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G33" s="10">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="13">
+        <v>73</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="G34" s="27">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="B35" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="1">
+        <v>62</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G35" s="3">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="5">
         <v>36</v>
       </c>
-      <c r="G5" s="7">
-        <v>-0.02</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="13">
-        <v>12</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="14">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="13">
-        <v>31</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7" s="14">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="3">
-        <v>33</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G8" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="3">
-        <v>21</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="G9" s="7">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="13">
-        <v>81</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="G10" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="C11" s="13">
-        <v>25</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="G11" s="14">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C12" s="3">
-        <v>8</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G12" s="7">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="13">
-        <v>7</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="G13" s="14">
-        <v>-0.02</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" s="13">
-        <v>17</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G14" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="3">
-        <v>19</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G15" s="7">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C16" s="3">
-        <v>29</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="G16" s="7">
-        <v>-0.03</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="13">
-        <v>10</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G17" s="14">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="C18" s="13">
-        <v>9</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="G18" s="14">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C19" s="3">
-        <v>29</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G19" s="7">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C20" s="3">
-        <v>59</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="G20" s="7">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C21" s="13">
-        <v>40</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="G21" s="14">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="13">
-        <v>73</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="G22" s="15">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C23" s="3">
-        <v>10</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F23" s="3" t="s">
+      <c r="D36" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F36" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="G23" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="3">
-        <v>26</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G24" s="7">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C25" s="13">
-        <v>23</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="F25" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="G25" s="15">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="C26" s="13">
-        <v>74</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="F26" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="G26" s="15">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C27" s="3">
-        <v>11</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G27" s="7">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C28" s="3">
-        <v>35</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="G28" s="7">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B29" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C29" s="13">
-        <v>18</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="G29" s="14">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="C30" s="13">
-        <v>24</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G30" s="14">
-        <v>-0.02</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C31" s="3">
-        <v>25</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G31" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="3">
-        <v>43</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="G32" s="11">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B33" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C33" s="13">
-        <v>5</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="G33" s="14">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B34" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="17">
-        <v>4</v>
-      </c>
-      <c r="D34" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="E34" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="F34" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="G34" s="18">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C35" s="3">
-        <v>62</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G35" s="7">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="9">
-        <v>36</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="G36" s="10">
+      <c r="G36" s="6">
         <v>0.01</v>
       </c>
     </row>
